--- a/data/vendor-search/results_all_sleeptracker.xlsx
+++ b/data/vendor-search/results_all_sleeptracker.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>cpe_strings</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>matched_terms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,8 +477,10 @@
       <c r="D2" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="E2" t="n">
-        <v>2</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -483,6 +490,11 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>cpe:2.3:a:garmin:garmin_communicator_plugin:2.6.4.0:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>garmin</t>
         </is>
       </c>
     </row>
@@ -505,8 +517,10 @@
       <c r="D3" t="n">
         <v>7.5</v>
       </c>
-      <c r="E3" t="n">
-        <v>3</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
@@ -514,6 +528,11 @@
           <t>cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:tvos:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>apple watch</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -534,8 +553,10 @@
       <c r="D4" t="n">
         <v>6.5</v>
       </c>
-      <c r="E4" t="n">
-        <v>3</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -545,6 +566,11 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>cpe:2.3:o:fitbit:charge_2_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:fitbit:charge_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>fitbit</t>
         </is>
       </c>
     </row>
@@ -567,8 +593,10 @@
       <c r="D5" t="n">
         <v>7.5</v>
       </c>
-      <c r="E5" t="n">
-        <v>3.1</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -578,6 +606,11 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>cpe:2.3:a:garmin:connect:4.61:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>garmin</t>
         </is>
       </c>
     </row>
@@ -600,8 +633,10 @@
       <c r="D6" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E6" t="n">
-        <v>3.1</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -611,6 +646,11 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>cpe:2.3:a:garmin:connect-iq:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>garmin</t>
         </is>
       </c>
     </row>
@@ -633,8 +673,10 @@
       <c r="D7" t="n">
         <v>7.5</v>
       </c>
-      <c r="E7" t="n">
-        <v>3.1</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -644,6 +686,11 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>cpe:2.3:a:garmin:connect-iq:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>garmin</t>
         </is>
       </c>
     </row>
@@ -666,8 +713,10 @@
       <c r="D8" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E8" t="n">
-        <v>3.1</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -677,6 +726,11 @@
       <c r="G8" t="inlineStr">
         <is>
           <t>cpe:2.3:a:garmin:connect-iq:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>garmin</t>
         </is>
       </c>
     </row>
@@ -699,8 +753,10 @@
       <c r="D9" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E9" t="n">
-        <v>3.1</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -710,6 +766,11 @@
       <c r="G9" t="inlineStr">
         <is>
           <t>cpe:2.3:a:garmin:connect-iq:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>garmin</t>
         </is>
       </c>
     </row>
@@ -732,8 +793,10 @@
       <c r="D10" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E10" t="n">
-        <v>3.1</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -743,6 +806,11 @@
       <c r="G10" t="inlineStr">
         <is>
           <t>cpe:2.3:a:garmin:connect-iq:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>garmin</t>
         </is>
       </c>
     </row>
@@ -765,8 +833,10 @@
       <c r="D11" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E11" t="n">
-        <v>3.1</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -776,6 +846,11 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>cpe:2.3:a:garmin:connect-iq:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>garmin</t>
         </is>
       </c>
     </row>
@@ -798,8 +873,10 @@
       <c r="D12" t="n">
         <v>9.1</v>
       </c>
-      <c r="E12" t="n">
-        <v>3.1</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -809,6 +886,11 @@
       <c r="G12" t="inlineStr">
         <is>
           <t>cpe:2.3:a:garmin:connect-iq:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>garmin</t>
         </is>
       </c>
     </row>
@@ -831,8 +913,10 @@
       <c r="D13" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E13" t="n">
-        <v>3.1</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -842,6 +926,11 @@
       <c r="G13" t="inlineStr">
         <is>
           <t>cpe:2.3:a:garmin:connect-iq:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>garmin</t>
         </is>
       </c>
     </row>
@@ -864,8 +953,10 @@
       <c r="D14" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E14" t="n">
-        <v>3.1</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -875,6 +966,11 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>cpe:2.3:a:garmin:connect-iq:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>garmin</t>
         </is>
       </c>
     </row>
@@ -897,13 +993,20 @@
       <c r="D15" t="n">
         <v>5.5</v>
       </c>
-      <c r="E15" t="n">
-        <v>3.1</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:watchos:*:*:*:*:*:*:*:*|cpe:2.3:h:apple:watch_ultra:-:*:*:*:*:*:*:*|cpe:2.3:h:apple:watch_ultra_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>apple watch</t>
         </is>
       </c>
     </row>
@@ -931,8 +1034,10 @@
       <c r="D16" t="n">
         <v>8.1</v>
       </c>
-      <c r="E16" t="n">
-        <v>3.1</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -940,6 +1045,11 @@
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>apple watch</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -960,8 +1070,10 @@
       <c r="D17" t="n">
         <v>9.9</v>
       </c>
-      <c r="E17" t="n">
-        <v>3.1</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -971,6 +1083,11 @@
       <c r="G17" t="inlineStr">
         <is>
           <t>cpe:2.3:o:garmin:forerunner_235_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:garmin:forerunner_235:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>garmin</t>
         </is>
       </c>
     </row>
@@ -993,8 +1110,10 @@
       <c r="D18" t="n">
         <v>9.9</v>
       </c>
-      <c r="E18" t="n">
-        <v>3.1</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1004,6 +1123,11 @@
       <c r="G18" t="inlineStr">
         <is>
           <t>cpe:2.3:o:garmin:forerunner_235_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:garmin:forerunner_235:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>garmin</t>
         </is>
       </c>
     </row>
@@ -1026,8 +1150,10 @@
       <c r="D19" t="n">
         <v>9.9</v>
       </c>
-      <c r="E19" t="n">
-        <v>3.1</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1037,6 +1163,11 @@
       <c r="G19" t="inlineStr">
         <is>
           <t>cpe:2.3:o:garmin:forerunner_235_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:garmin:forerunner_235:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>garmin</t>
         </is>
       </c>
     </row>
@@ -1059,8 +1190,10 @@
       <c r="D20" t="n">
         <v>9.9</v>
       </c>
-      <c r="E20" t="n">
-        <v>3.1</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1070,6 +1203,11 @@
       <c r="G20" t="inlineStr">
         <is>
           <t>cpe:2.3:o:garmin:forerunner_235_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:garmin:forerunner_235:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>garmin</t>
         </is>
       </c>
     </row>
@@ -1092,8 +1230,10 @@
       <c r="D21" t="n">
         <v>2.4</v>
       </c>
-      <c r="E21" t="n">
-        <v>3.1</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
@@ -1101,6 +1241,11 @@
           <t>cpe:2.3:o:apple:ipados:*:*:*:*:*:*:*:*|cpe:2.3:o:apple:iphone_os:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>apple watch</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1121,8 +1266,10 @@
       <c r="D22" t="n">
         <v>2.4</v>
       </c>
-      <c r="E22" t="n">
-        <v>3.1</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
@@ -1130,6 +1277,11 @@
           <t>cpe:2.3:o:apple:watchos:*:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>apple watch</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1150,8 +1302,10 @@
       <c r="D23" t="n">
         <v>5.9</v>
       </c>
-      <c r="E23" t="n">
-        <v>3.1</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1161,6 +1315,11 @@
       <c r="G23" t="inlineStr">
         <is>
           <t>cpe:2.3:a:samsung:internet:5.0.9:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>samsung galaxy watch</t>
         </is>
       </c>
     </row>
@@ -1183,8 +1342,10 @@
       <c r="D24" t="n">
         <v>4.6</v>
       </c>
-      <c r="E24" t="n">
-        <v>3.1</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1194,6 +1355,11 @@
       <c r="G24" t="inlineStr">
         <is>
           <t>cpe:2.3:o:apple:watchos:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>apple watch</t>
         </is>
       </c>
     </row>
@@ -1216,8 +1382,10 @@
       <c r="D25" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E25" t="n">
-        <v>3.1</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1227,6 +1395,11 @@
       <c r="G25" t="inlineStr">
         <is>
           <t>cpe:2.3:o:mobvoi:tichome_mini_firmware:012-18853:*:*:*:*:*:*:*|cpe:2.3:o:mobvoi:tichome_mini_firmware:027-58389:*:*:*:*:*:*:*|cpe:2.3:h:mobvoi:tichome_mini:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>mobvoi</t>
         </is>
       </c>
     </row>
@@ -1249,8 +1422,10 @@
       <c r="D26" t="n">
         <v>7.5</v>
       </c>
-      <c r="E26" t="n">
-        <v>3.1</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1260,6 +1435,11 @@
       <c r="G26" t="inlineStr">
         <is>
           <t>cpe:2.3:o:garmin:empirbus_wireless_display_unit_firmware:1.4.6:*:*:*:*:*:*:*|cpe:2.3:h:garmin:empirbus_wireless_display_unit:v1:*:*:*:*:*:*:*|cpe:2.3:o:garmin:empirbus_wireless_display_unit_firmware:5.00:*:*:*:*:*:*:*|cpe:2.3:h:garmin:empirbus_wireless_display_unit:v2:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>garmin</t>
         </is>
       </c>
     </row>
@@ -1282,8 +1462,10 @@
       <c r="D27" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="E27" t="n">
-        <v>3.1</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1293,6 +1475,11 @@
       <c r="G27" t="inlineStr">
         <is>
           <t>cpe:2.3:o:garmin:empirbus_wireless_display_unit_firmware:1.4.6:*:*:*:*:*:*:*|cpe:2.3:h:garmin:empirbus_wireless_display_unit:v1:*:*:*:*:*:*:*|cpe:2.3:o:garmin:empirbus_wireless_display_unit_firmware:5.00:*:*:*:*:*:*:*|cpe:2.3:h:garmin:empirbus_wireless_display_unit:v2:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>garmin</t>
         </is>
       </c>
     </row>
@@ -1315,8 +1502,10 @@
       <c r="D28" t="n">
         <v>5</v>
       </c>
-      <c r="E28" t="n">
-        <v>3.1</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1326,6 +1515,11 @@
       <c r="G28" t="inlineStr">
         <is>
           <t>cpe:2.3:o:garmin:empirbus_wireless_display_unit_firmware:1.4.6:*:*:*:*:*:*:*|cpe:2.3:h:garmin:empirbus_wireless_display_unit:v1:*:*:*:*:*:*:*|cpe:2.3:o:garmin:empirbus_wireless_display_unit_firmware:5.00:*:*:*:*:*:*:*|cpe:2.3:h:garmin:empirbus_wireless_display_unit:v2:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>garmin</t>
         </is>
       </c>
     </row>
@@ -1348,8 +1542,10 @@
       <c r="D29" t="n">
         <v>7.3</v>
       </c>
-      <c r="E29" t="n">
-        <v>3.1</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1359,6 +1555,11 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>cpe:2.3:o:garmin:empirbus_wireless_display_unit_firmware:1.4.6:*:*:*:*:*:*:*|cpe:2.3:h:garmin:empirbus_wireless_display_unit:v1:*:*:*:*:*:*:*|cpe:2.3:o:garmin:empirbus_wireless_display_unit_firmware:5.00:*:*:*:*:*:*:*|cpe:2.3:h:garmin:empirbus_wireless_display_unit:v2:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>garmin</t>
         </is>
       </c>
     </row>
